--- a/server/uploads/1778735015919-activity_india_foreign (1).xlsx
+++ b/server/uploads/1778735015919-activity_india_foreign (1).xlsx
@@ -449,7 +449,7 @@
         <v>Activity</v>
       </c>
       <c r="F2" t="str">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="G2" t="str">
         <v>INR</v>
